--- a/docs/downloads/11/tbl_degats_stocks_riz_marovoay_maroala.xlsx
+++ b/docs/downloads/11/tbl_degats_stocks_riz_marovoay_maroala.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -410,7 +410,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C3">
@@ -431,7 +431,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C4">
@@ -447,12 +447,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C5">
@@ -468,19 +468,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -494,7 +494,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Criquets</t>
         </is>
       </c>
       <c r="C7">
@@ -515,14 +515,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C8">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -536,7 +536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C9">
@@ -557,14 +557,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -578,7 +578,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C11">
@@ -599,17 +599,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C12">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>54.3</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="13">
@@ -620,58 +620,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>40</v>
-      </c>
-      <c r="D14">
-        <v>54.3</v>
-      </c>
-      <c r="E14">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>93.3</v>
-      </c>
-      <c r="D15">
-        <v>3.6</v>
-      </c>
-      <c r="E15">
         <v>3.1</v>
       </c>
     </row>
